--- a/macro/naver.xlsx
+++ b/macro/naver.xlsx
@@ -1,46 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20411"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\stack-overflow\macro\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73ED803D-9B7A-4B36-8E2F-2EB28682D8F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12323" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="url" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="id_pw" sheetId="2" r:id="rId5"/>
+    <sheet name="id_pw" sheetId="2" r:id="rId1"/>
+    <sheet name="urls" sheetId="1" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>https://blog.naver.com/tripholic_jiny/222696185505</t>
   </si>
   <si>
-    <t>chlendyd7</t>
-  </si>
-  <si>
-    <t>d4632077zZ@</t>
+    <t>5)wt)2ho</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">cam78030 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6*st(4pa</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mit561540</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6)ov&amp;7kg</t>
+  </si>
+  <si>
+    <t>dan619974</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0*ci*0wg</t>
+  </si>
+  <si>
+    <t>pri390277</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4%hd#5cg</t>
+  </si>
+  <si>
+    <t>ble258469</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://blog.naver.com/loye7121/221906072179</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
-    <font>
-      <sz val="10.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
-    </font>
-    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -49,43 +118,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -275,45 +349,90 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="A1"/>
-  </hyperlinks>
-  <drawing r:id="rId2"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{79F2FB7E-EC1E-41A7-A4B1-6C343BB64AF4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/macro/naver.xlsx
+++ b/macro/naver.xlsx
@@ -8,81 +8,96 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\stack-overflow\macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73ED803D-9B7A-4B36-8E2F-2EB28682D8F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF28C11E-6C28-4A20-808A-13A6A76CB305}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12323" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12323" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="id_pw" sheetId="2" r:id="rId1"/>
     <sheet name="urls" sheetId="1" r:id="rId2"/>
+    <sheet name="educated_person" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="url">educated_person!$A:$A</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>5)wt)2ho</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">cam78030 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>6*st(4pa</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mit561540</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dan619974</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0*ci*0wg</t>
+  </si>
+  <si>
+    <t>pri390277</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ble258469</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
   <si>
     <t>https://blog.naver.com/tripholic_jiny/222696185505</t>
-  </si>
-  <si>
-    <t>5)wt)2ho</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">cam78030 </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>6*st(4pa</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mit561540</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://blog.naver.com/loye7121/221906072179</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://kin.naver.com/qna/detail.naver?d1id=11&amp;dirId=11080305&amp;docId=455516979&amp;enc=utf8&amp;kinsrch_src=pc_nx_kin&amp;qb=7KeA7Iud7J24IOyYgeyWtOuhnA%3D%3D&amp;rank=1&amp;search_sort=0&amp;section=kin.qna_ency_cafe&amp;spq=0</t>
+  </si>
+  <si>
+    <t>#p172088188579384906755</t>
+  </si>
+  <si>
+    <t>chlendyd7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>d4632077zZ@</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4%hd#5cg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>6)ov&amp;7kg</t>
-  </si>
-  <si>
-    <t>dan619974</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0*ci*0wg</t>
-  </si>
-  <si>
-    <t>pri390277</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>4%hd#5cg</t>
-  </si>
-  <si>
-    <t>ble258469</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://blog.naver.com/loye7121/221906072179</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -132,14 +147,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -359,51 +373,76 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -417,22 +456,41 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1" spans="1:1" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
+      <c r="A2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{79F2FB7E-EC1E-41A7-A4B1-6C343BB64AF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D56ACE-33DB-45CD-84A7-276F464F089E}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>